--- a/public/samples/ko/sample2.xlsx
+++ b/public/samples/ko/sample2.xlsx
@@ -447,7 +447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -468,6 +468,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -483,9 +486,12 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>특수교육 대상</v>
+        <v>국어 수준</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>학습 지원</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>이전 반</v>
       </c>
     </row>
@@ -494,7 +500,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>이서연</v>
+        <v>한서연</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>여</v>
@@ -502,11 +508,14 @@
       <c r="D3" s="2">
         <v>75</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="4">
@@ -514,19 +523,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>김민준</v>
+        <v>안민준</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D4" s="2">
-        <v>87</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>3반</v>
+        <v>✓</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +546,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>한지우</v>
+        <v>이지우</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D5" s="2">
-        <v>73</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +569,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>오서준</v>
+        <v>류서준</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D6" s="2">
-        <v>79</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="7">
@@ -574,19 +592,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>박서윤</v>
+        <v>권서윤</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D7" s="2">
-        <v>74</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="8">
@@ -600,13 +621,16 @@
         <v>남</v>
       </c>
       <c r="D8" s="2">
-        <v>95</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="9">
@@ -614,18 +638,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>한하은</v>
+        <v>조하은</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D9" s="2">
-        <v>85</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -634,19 +661,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>정예준</v>
+        <v>김예준</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D10" s="2">
-        <v>69</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>68</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="11">
@@ -654,19 +684,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>서민서</v>
+        <v>황민서</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D11" s="2">
-        <v>73</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
+        <v>80</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="12">
@@ -674,18 +707,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>신시우</v>
+        <v>한시우</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D12" s="2">
-        <v>63</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>68</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
         <v>3반</v>
       </c>
     </row>
@@ -700,13 +736,16 @@
         <v>여</v>
       </c>
       <c r="D13" s="2">
-        <v>80</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="14">
@@ -714,18 +753,21 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>최하준</v>
+        <v>이하준</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D14" s="2">
-        <v>88</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -734,18 +776,21 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>임윤서</v>
+        <v>이윤서</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D15" s="2">
-        <v>80</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -754,18 +799,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>이주원</v>
+        <v>신주원</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D16" s="2">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -774,19 +822,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>박채원</v>
+        <v>김채원</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D17" s="2">
-        <v>79</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="18">
@@ -794,19 +845,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>박지호</v>
+        <v>이지호</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D18" s="2">
-        <v>72</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="19">
@@ -814,19 +868,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>이수아</v>
+        <v>정수아</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D19" s="2">
-        <v>78</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="20">
@@ -834,19 +891,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>오지후</v>
+        <v>강지후</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D20" s="2">
-        <v>66</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>93</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="21">
@@ -854,19 +914,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>홍지민</v>
+        <v>정지민</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D21" s="2">
-        <v>83</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v>✓</v>
+        <v>75</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="22">
@@ -874,19 +937,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>송준우</v>
+        <v>홍준우</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D22" s="2">
-        <v>78</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +960,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>강예은</v>
+        <v>박예은</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D23" s="2">
-        <v>85</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +983,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>정건우</v>
+        <v>최건우</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D24" s="2">
-        <v>75</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="25">
@@ -934,18 +1006,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>정다은</v>
+        <v>임다은</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D25" s="2">
-        <v>77</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -954,19 +1029,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>박우진</v>
+        <v>황우진</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D26" s="2">
-        <v>86</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>63</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +1052,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>송하린</v>
+        <v>조하린</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D27" s="2">
-        <v>66</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="28">
@@ -994,19 +1075,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>김선우</v>
+        <v>최선우</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D28" s="2">
-        <v>75</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="29">
@@ -1014,19 +1098,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>정소율</v>
+        <v>임소율</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D29" s="2">
-        <v>96</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>87</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="30">
@@ -1034,19 +1121,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>황현우</v>
+        <v>오현우</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D30" s="2">
-        <v>74</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>3반</v>
+        <v>✓</v>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="31">
@@ -1054,18 +1144,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>한유나</v>
+        <v>최유나</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D31" s="2">
-        <v>71</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E31" s="2">
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1074,19 +1167,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>한연우</v>
+        <v>박연우</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D32" s="2">
-        <v>78</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>96</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="33">
@@ -1094,18 +1190,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>임시은</v>
+        <v>강시은</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D33" s="2">
-        <v>84</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>66</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5</v>
       </c>
       <c r="F33" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G33" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1114,19 +1213,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>송유준</v>
+        <v>김유준</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D34" s="2">
-        <v>72</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="35">
@@ -1134,19 +1236,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>황예린</v>
+        <v>오예린</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D35" s="2">
-        <v>74</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>90</v>
+      </c>
+      <c r="E35" s="2">
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="36">
@@ -1154,19 +1259,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>홍정우</v>
+        <v>조정우</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D36" s="2">
-        <v>76</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="37">
@@ -1174,19 +1282,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>박지안</v>
+        <v>최지안</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D37" s="2">
-        <v>90</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="38">
@@ -1194,19 +1305,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>장승현</v>
+        <v>이승현</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D38" s="2">
-        <v>66</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
-        <v>1반</v>
+        <v>✓</v>
+      </c>
+      <c r="G38" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="39">
@@ -1214,19 +1328,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>오서아</v>
+        <v>김서아</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D39" s="2">
-        <v>72</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="40">
@@ -1234,19 +1351,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>오민재</v>
+        <v>장민재</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D40" s="2">
-        <v>74</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="41">
@@ -1254,18 +1374,21 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>윤나은</v>
+        <v>신나은</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D41" s="2">
-        <v>77</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>66</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
         <v>4반</v>
       </c>
     </row>
@@ -1274,19 +1397,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>장지환</v>
+        <v>최지환</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D42" s="2">
-        <v>79</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>2반</v>
+        <v>✓</v>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="43">
@@ -1294,18 +1420,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>홍서연</v>
+        <v>박서연</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D43" s="2">
-        <v>77</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -1314,19 +1443,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>이민준</v>
+        <v>강민준</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D44" s="2">
-        <v>62</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v>✓</v>
+        <v>76</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="45">
@@ -1334,19 +1466,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>박지우</v>
+        <v>홍지우</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D45" s="2">
-        <v>83</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>94</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="46">
@@ -1354,19 +1489,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>최서준</v>
+        <v>김서준</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D46" s="2">
-        <v>77</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="47">
@@ -1374,19 +1512,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>임서윤</v>
+        <v>황하은</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D47" s="2">
-        <v>65</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>66</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="48">
@@ -1394,19 +1535,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>조도윤</v>
+        <v>홍도윤</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D48" s="2">
-        <v>86</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="49">
@@ -1414,19 +1558,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>류하은</v>
+        <v>서민서</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D49" s="2">
-        <v>60</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E49" s="2">
+        <v>5</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="50">
@@ -1434,19 +1581,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>윤예준</v>
+        <v>오예준</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D50" s="2">
-        <v>59</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>89</v>
+      </c>
+      <c r="E50" s="2">
+        <v>5</v>
       </c>
       <c r="F50" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="51">
@@ -1454,18 +1604,21 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>강민서</v>
+        <v>조지유</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D51" s="2">
-        <v>79</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
         <v>3반</v>
       </c>
     </row>
@@ -1474,19 +1627,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>김시우</v>
+        <v>안시우</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D52" s="2">
-        <v>94</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="53">
@@ -1494,18 +1650,21 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>홍지유</v>
+        <v>이채원</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D53" s="2">
-        <v>81</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>67</v>
+      </c>
+      <c r="E53" s="2">
+        <v>4</v>
       </c>
       <c r="F53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -1514,19 +1673,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>류하준</v>
+        <v>신하준</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D54" s="2">
-        <v>68</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="55">
@@ -1534,18 +1696,21 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>강윤서</v>
+        <v>장수아</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D55" s="2">
-        <v>86</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>88</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
       </c>
       <c r="F55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str">
         <v>3반</v>
       </c>
     </row>
@@ -1554,19 +1719,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>윤주원</v>
+        <v>최주원</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D56" s="2">
-        <v>73</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>96</v>
+      </c>
+      <c r="E56" s="2">
+        <v>5</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="57">
@@ -1574,19 +1742,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>서채원</v>
+        <v>박지민</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D57" s="2">
-        <v>94</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>88</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="58">
@@ -1594,19 +1765,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>오지호</v>
+        <v>안지호</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D58" s="2">
-        <v>89</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="E58" s="2">
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="59">
@@ -1614,19 +1788,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>황수아</v>
+        <v>최예은</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D59" s="2">
-        <v>80</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E59" s="2">
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="60">
@@ -1634,19 +1811,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>안지후</v>
+        <v>오지후</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D60" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E60" s="2">
+        <v>4</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="61">
@@ -1654,19 +1834,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>조지민</v>
+        <v>송다은</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D61" s="2">
-        <v>72</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E61" s="2">
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="62">
@@ -1674,19 +1857,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>황준우</v>
+        <v>오준우</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D62" s="2">
-        <v>76</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v>✓</v>
+        <v>78</v>
+      </c>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="63">
@@ -1694,19 +1880,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>신예은</v>
+        <v>홍하린</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D63" s="2">
-        <v>68</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>2반</v>
+        <v>✓</v>
+      </c>
+      <c r="G63" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="64">
@@ -1720,12 +1909,15 @@
         <v>남</v>
       </c>
       <c r="D64" s="2">
-        <v>88</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1734,19 +1926,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>서다은</v>
+        <v>김소율</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D65" s="2">
-        <v>88</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E65" s="2">
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="66">
@@ -1754,19 +1949,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>조우진</v>
+        <v>안우진</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D66" s="2">
-        <v>81</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="67">
@@ -1774,19 +1972,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>황하린</v>
+        <v>류유나</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D67" s="2">
-        <v>74</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E67" s="2">
+        <v>2</v>
       </c>
       <c r="F67" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G67" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="68">
@@ -1800,13 +2001,16 @@
         <v>남</v>
       </c>
       <c r="D68" s="2">
-        <v>79</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="69">
@@ -1814,18 +2018,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>최소율</v>
+        <v>박시은</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D69" s="2">
-        <v>72</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -1834,19 +2041,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>오현우</v>
+        <v>안현우</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D70" s="2">
-        <v>80</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E70" s="2">
+        <v>4</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="71">
@@ -1854,18 +2064,21 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>임유나</v>
+        <v>장예린</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D71" s="2">
-        <v>77</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
         <v>4반</v>
       </c>
     </row>
@@ -1874,19 +2087,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>안연우</v>
+        <v>강연우</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D72" s="2">
-        <v>89</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E72" s="2">
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="73">
@@ -1894,19 +2110,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>정시은</v>
+        <v>홍지안</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D73" s="2">
-        <v>81</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="74">
@@ -1920,13 +2139,16 @@
         <v>남</v>
       </c>
       <c r="D74" s="2">
-        <v>78</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="75">
@@ -1934,18 +2156,21 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>최예린</v>
+        <v>서서아</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D75" s="2">
-        <v>77</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E75" s="2">
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G75" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1954,19 +2179,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>오정우</v>
+        <v>홍정우</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D76" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="77">
@@ -1974,19 +2202,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>안지안</v>
+        <v>최나은</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D77" s="2">
-        <v>71</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>63</v>
+      </c>
+      <c r="E77" s="2">
+        <v>3</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="78">
@@ -1994,19 +2225,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>조승현</v>
+        <v>신승현</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D78" s="2">
-        <v>84</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="79">
@@ -2014,18 +2248,21 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>윤서아</v>
+        <v>최지우</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D79" s="2">
-        <v>82</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E79" s="2">
+        <v>4</v>
       </c>
       <c r="F79" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -2034,19 +2271,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>송민재</v>
+        <v>안민재</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D80" s="2">
-        <v>70</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E80" s="2">
+        <v>4</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="81">
@@ -2054,19 +2294,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>조나은</v>
+        <v>신서윤</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D81" s="2">
-        <v>67</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="82">
@@ -2074,24 +2317,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>신지환</v>
+        <v>황지환</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D82" s="2">
-        <v>86</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2102,13 +2348,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C1" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2124,21 +2370,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B1" s="2">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/public/samples/ko/sample2.xlsx
+++ b/public/samples/ko/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="학생 명단" sheetId="2" r:id="rId2"/>
     <sheet name="같은 반 배정" sheetId="3" r:id="rId3"/>
     <sheet name="분리 배정" sheetId="4" r:id="rId4"/>
+    <sheet name="항목" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -2392,4 +2393,84 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>종류</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>선택지</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>성별</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>남</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>여</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>학업 성취도</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>숫자</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>국어 수준</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>정도</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>학습 지원</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>이전 반</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>1반</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>2반</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>3반</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>4반</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/public/samples/ko/sample2.xlsx
+++ b/public/samples/ko/sample2.xlsx
@@ -7,6 +7,7 @@
     <sheet name="학생 명단" sheetId="2" r:id="rId2"/>
     <sheet name="같은 반 배정" sheetId="3" r:id="rId3"/>
     <sheet name="분리 배정" sheetId="4" r:id="rId4"/>
+    <sheet name="항목" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -447,7 +448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:G82"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="str">
@@ -468,6 +469,9 @@
       <c r="F1" s="2">
         <v>1</v>
       </c>
+      <c r="G1" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="str">
@@ -483,9 +487,12 @@
         <v>학업 성취도</v>
       </c>
       <c r="E2" s="2" t="str">
-        <v>특수교육 대상</v>
+        <v>국어 수준</v>
       </c>
       <c r="F2" s="2" t="str">
+        <v>학습 지원</v>
+      </c>
+      <c r="G2" s="2" t="str">
         <v>이전 반</v>
       </c>
     </row>
@@ -494,7 +501,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>이서연</v>
+        <v>한서연</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>여</v>
@@ -502,11 +509,14 @@
       <c r="D3" s="2">
         <v>75</v>
       </c>
-      <c r="E3" s="2" t="str">
-        <v/>
+      <c r="E3" s="2">
+        <v>3</v>
       </c>
       <c r="F3" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G3" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="4">
@@ -514,19 +524,22 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>김민준</v>
+        <v>안민준</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D4" s="2">
-        <v>87</v>
-      </c>
-      <c r="E4" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="str">
-        <v>3반</v>
+        <v>✓</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="5">
@@ -534,19 +547,22 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>한지우</v>
+        <v>이지우</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D5" s="2">
-        <v>73</v>
-      </c>
-      <c r="E5" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="6">
@@ -554,19 +570,22 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>오서준</v>
+        <v>류서준</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D6" s="2">
-        <v>79</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="7">
@@ -574,19 +593,22 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>박서윤</v>
+        <v>권서윤</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D7" s="2">
-        <v>74</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4</v>
       </c>
       <c r="F7" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="8">
@@ -600,13 +622,16 @@
         <v>남</v>
       </c>
       <c r="D8" s="2">
-        <v>95</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="9">
@@ -614,18 +639,21 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>한하은</v>
+        <v>조하은</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D9" s="2">
-        <v>85</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G9" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -634,19 +662,22 @@
         <v>8</v>
       </c>
       <c r="B10" s="2" t="str">
-        <v>정예준</v>
+        <v>김예준</v>
       </c>
       <c r="C10" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D10" s="2">
-        <v>69</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <v/>
+        <v>68</v>
+      </c>
+      <c r="E10" s="2">
+        <v>4</v>
       </c>
       <c r="F10" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="11">
@@ -654,19 +685,22 @@
         <v>9</v>
       </c>
       <c r="B11" s="2" t="str">
-        <v>서민서</v>
+        <v>황민서</v>
       </c>
       <c r="C11" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D11" s="2">
-        <v>73</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <v>✓</v>
+        <v>80</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
       </c>
       <c r="F11" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="12">
@@ -674,18 +708,21 @@
         <v>10</v>
       </c>
       <c r="B12" s="2" t="str">
-        <v>신시우</v>
+        <v>한시우</v>
       </c>
       <c r="C12" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D12" s="2">
-        <v>63</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <v/>
+        <v>68</v>
+      </c>
+      <c r="E12" s="2">
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G12" s="2" t="str">
         <v>3반</v>
       </c>
     </row>
@@ -700,13 +737,16 @@
         <v>여</v>
       </c>
       <c r="D13" s="2">
-        <v>80</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
       </c>
       <c r="F13" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G13" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="14">
@@ -714,18 +754,21 @@
         <v>12</v>
       </c>
       <c r="B14" s="2" t="str">
-        <v>최하준</v>
+        <v>이하준</v>
       </c>
       <c r="C14" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D14" s="2">
-        <v>88</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E14" s="2">
+        <v>3</v>
       </c>
       <c r="F14" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G14" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -734,18 +777,21 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="str">
-        <v>임윤서</v>
+        <v>이윤서</v>
       </c>
       <c r="C15" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D15" s="2">
-        <v>80</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
       </c>
       <c r="F15" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G15" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -754,18 +800,21 @@
         <v>14</v>
       </c>
       <c r="B16" s="2" t="str">
-        <v>이주원</v>
+        <v>신주원</v>
       </c>
       <c r="C16" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D16" s="2">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
       </c>
       <c r="F16" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G16" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -774,19 +823,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2" t="str">
-        <v>박채원</v>
+        <v>김채원</v>
       </c>
       <c r="C17" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D17" s="2">
-        <v>79</v>
-      </c>
-      <c r="E17" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G17" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="18">
@@ -794,19 +846,22 @@
         <v>16</v>
       </c>
       <c r="B18" s="2" t="str">
-        <v>박지호</v>
+        <v>이지호</v>
       </c>
       <c r="C18" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D18" s="2">
-        <v>72</v>
-      </c>
-      <c r="E18" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G18" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="19">
@@ -814,19 +869,22 @@
         <v>17</v>
       </c>
       <c r="B19" s="2" t="str">
-        <v>이수아</v>
+        <v>정수아</v>
       </c>
       <c r="C19" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D19" s="2">
-        <v>78</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
       </c>
       <c r="F19" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G19" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="20">
@@ -834,19 +892,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="2" t="str">
-        <v>오지후</v>
+        <v>강지후</v>
       </c>
       <c r="C20" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D20" s="2">
-        <v>66</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <v/>
+        <v>93</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G20" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="21">
@@ -854,19 +915,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="2" t="str">
-        <v>홍지민</v>
+        <v>정지민</v>
       </c>
       <c r="C21" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D21" s="2">
-        <v>83</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <v>✓</v>
+        <v>75</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
       </c>
       <c r="F21" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G21" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="22">
@@ -874,19 +938,22 @@
         <v>20</v>
       </c>
       <c r="B22" s="2" t="str">
-        <v>송준우</v>
+        <v>홍준우</v>
       </c>
       <c r="C22" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D22" s="2">
-        <v>78</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
       </c>
       <c r="F22" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="23">
@@ -894,19 +961,22 @@
         <v>21</v>
       </c>
       <c r="B23" s="2" t="str">
-        <v>강예은</v>
+        <v>박예은</v>
       </c>
       <c r="C23" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D23" s="2">
-        <v>85</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
       </c>
       <c r="F23" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="24">
@@ -914,19 +984,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="2" t="str">
-        <v>정건우</v>
+        <v>최건우</v>
       </c>
       <c r="C24" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D24" s="2">
-        <v>75</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
       </c>
       <c r="F24" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G24" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="25">
@@ -934,18 +1007,21 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="str">
-        <v>정다은</v>
+        <v>임다은</v>
       </c>
       <c r="C25" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D25" s="2">
-        <v>77</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E25" s="2">
+        <v>4</v>
       </c>
       <c r="F25" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G25" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -954,19 +1030,22 @@
         <v>24</v>
       </c>
       <c r="B26" s="2" t="str">
-        <v>박우진</v>
+        <v>황우진</v>
       </c>
       <c r="C26" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D26" s="2">
-        <v>86</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v/>
+        <v>63</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
       </c>
       <c r="F26" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G26" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="27">
@@ -974,19 +1053,22 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="str">
-        <v>송하린</v>
+        <v>조하린</v>
       </c>
       <c r="C27" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D27" s="2">
-        <v>66</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E27" s="2">
+        <v>3</v>
       </c>
       <c r="F27" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G27" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="28">
@@ -994,19 +1076,22 @@
         <v>26</v>
       </c>
       <c r="B28" s="2" t="str">
-        <v>김선우</v>
+        <v>최선우</v>
       </c>
       <c r="C28" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D28" s="2">
-        <v>75</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
       </c>
       <c r="F28" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G28" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="29">
@@ -1014,19 +1099,22 @@
         <v>27</v>
       </c>
       <c r="B29" s="2" t="str">
-        <v>정소율</v>
+        <v>임소율</v>
       </c>
       <c r="C29" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D29" s="2">
-        <v>96</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v/>
+        <v>87</v>
+      </c>
+      <c r="E29" s="2">
+        <v>3</v>
       </c>
       <c r="F29" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G29" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="30">
@@ -1034,19 +1122,22 @@
         <v>28</v>
       </c>
       <c r="B30" s="2" t="str">
-        <v>황현우</v>
+        <v>오현우</v>
       </c>
       <c r="C30" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D30" s="2">
-        <v>74</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E30" s="2">
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="str">
-        <v>3반</v>
+        <v>✓</v>
+      </c>
+      <c r="G30" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="31">
@@ -1054,18 +1145,21 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="str">
-        <v>한유나</v>
+        <v>최유나</v>
       </c>
       <c r="C31" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D31" s="2">
-        <v>71</v>
-      </c>
-      <c r="E31" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E31" s="2">
+        <v>3</v>
       </c>
       <c r="F31" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G31" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1074,19 +1168,22 @@
         <v>30</v>
       </c>
       <c r="B32" s="2" t="str">
-        <v>한연우</v>
+        <v>박연우</v>
       </c>
       <c r="C32" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D32" s="2">
-        <v>78</v>
-      </c>
-      <c r="E32" s="2" t="str">
-        <v/>
+        <v>96</v>
+      </c>
+      <c r="E32" s="2">
+        <v>3</v>
       </c>
       <c r="F32" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G32" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="33">
@@ -1094,18 +1191,21 @@
         <v>31</v>
       </c>
       <c r="B33" s="2" t="str">
-        <v>임시은</v>
+        <v>강시은</v>
       </c>
       <c r="C33" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D33" s="2">
-        <v>84</v>
-      </c>
-      <c r="E33" s="2" t="str">
-        <v/>
+        <v>66</v>
+      </c>
+      <c r="E33" s="2">
+        <v>5</v>
       </c>
       <c r="F33" s="2" t="str">
+        <v>✓</v>
+      </c>
+      <c r="G33" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1114,19 +1214,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="str">
-        <v>송유준</v>
+        <v>김유준</v>
       </c>
       <c r="C34" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D34" s="2">
-        <v>72</v>
-      </c>
-      <c r="E34" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E34" s="2">
+        <v>3</v>
       </c>
       <c r="F34" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G34" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="35">
@@ -1134,19 +1237,22 @@
         <v>33</v>
       </c>
       <c r="B35" s="2" t="str">
-        <v>황예린</v>
+        <v>오예린</v>
       </c>
       <c r="C35" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D35" s="2">
-        <v>74</v>
-      </c>
-      <c r="E35" s="2" t="str">
-        <v/>
+        <v>90</v>
+      </c>
+      <c r="E35" s="2">
+        <v>3</v>
       </c>
       <c r="F35" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G35" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="36">
@@ -1154,19 +1260,22 @@
         <v>34</v>
       </c>
       <c r="B36" s="2" t="str">
-        <v>홍정우</v>
+        <v>조정우</v>
       </c>
       <c r="C36" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D36" s="2">
-        <v>76</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
       </c>
       <c r="F36" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G36" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="37">
@@ -1174,19 +1283,22 @@
         <v>35</v>
       </c>
       <c r="B37" s="2" t="str">
-        <v>박지안</v>
+        <v>최지안</v>
       </c>
       <c r="C37" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D37" s="2">
-        <v>90</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G37" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="38">
@@ -1194,19 +1306,22 @@
         <v>36</v>
       </c>
       <c r="B38" s="2" t="str">
-        <v>장승현</v>
+        <v>이승현</v>
       </c>
       <c r="C38" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D38" s="2">
-        <v>66</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <v/>
+        <v>71</v>
+      </c>
+      <c r="E38" s="2">
+        <v>3</v>
       </c>
       <c r="F38" s="2" t="str">
-        <v>1반</v>
+        <v>✓</v>
+      </c>
+      <c r="G38" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="39">
@@ -1214,19 +1329,22 @@
         <v>37</v>
       </c>
       <c r="B39" s="2" t="str">
-        <v>오서아</v>
+        <v>김서아</v>
       </c>
       <c r="C39" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D39" s="2">
-        <v>72</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E39" s="2">
+        <v>3</v>
       </c>
       <c r="F39" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G39" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="40">
@@ -1234,19 +1352,22 @@
         <v>38</v>
       </c>
       <c r="B40" s="2" t="str">
-        <v>오민재</v>
+        <v>장민재</v>
       </c>
       <c r="C40" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D40" s="2">
-        <v>74</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E40" s="2">
+        <v>3</v>
       </c>
       <c r="F40" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G40" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="41">
@@ -1254,18 +1375,21 @@
         <v>39</v>
       </c>
       <c r="B41" s="2" t="str">
-        <v>윤나은</v>
+        <v>신나은</v>
       </c>
       <c r="C41" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D41" s="2">
-        <v>77</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <v/>
+        <v>66</v>
+      </c>
+      <c r="E41" s="2">
+        <v>3</v>
       </c>
       <c r="F41" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G41" s="2" t="str">
         <v>4반</v>
       </c>
     </row>
@@ -1274,19 +1398,22 @@
         <v>40</v>
       </c>
       <c r="B42" s="2" t="str">
-        <v>장지환</v>
+        <v>최지환</v>
       </c>
       <c r="C42" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D42" s="2">
-        <v>79</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
       </c>
       <c r="F42" s="2" t="str">
-        <v>2반</v>
+        <v>✓</v>
+      </c>
+      <c r="G42" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="43">
@@ -1294,18 +1421,21 @@
         <v>41</v>
       </c>
       <c r="B43" s="2" t="str">
-        <v>홍서연</v>
+        <v>박서연</v>
       </c>
       <c r="C43" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D43" s="2">
-        <v>77</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
       </c>
       <c r="F43" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G43" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -1314,19 +1444,22 @@
         <v>42</v>
       </c>
       <c r="B44" s="2" t="str">
-        <v>이민준</v>
+        <v>강민준</v>
       </c>
       <c r="C44" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D44" s="2">
-        <v>62</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <v>✓</v>
+        <v>76</v>
+      </c>
+      <c r="E44" s="2">
+        <v>3</v>
       </c>
       <c r="F44" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G44" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="45">
@@ -1334,19 +1467,22 @@
         <v>43</v>
       </c>
       <c r="B45" s="2" t="str">
-        <v>박지우</v>
+        <v>홍지우</v>
       </c>
       <c r="C45" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D45" s="2">
-        <v>83</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <v/>
+        <v>94</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2</v>
       </c>
       <c r="F45" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G45" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="46">
@@ -1354,19 +1490,22 @@
         <v>44</v>
       </c>
       <c r="B46" s="2" t="str">
-        <v>최서준</v>
+        <v>김서준</v>
       </c>
       <c r="C46" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D46" s="2">
-        <v>77</v>
-      </c>
-      <c r="E46" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2</v>
       </c>
       <c r="F46" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G46" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="47">
@@ -1374,19 +1513,22 @@
         <v>45</v>
       </c>
       <c r="B47" s="2" t="str">
-        <v>임서윤</v>
+        <v>황하은</v>
       </c>
       <c r="C47" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D47" s="2">
-        <v>65</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <v/>
+        <v>66</v>
+      </c>
+      <c r="E47" s="2">
+        <v>5</v>
       </c>
       <c r="F47" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G47" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="48">
@@ -1394,19 +1536,22 @@
         <v>46</v>
       </c>
       <c r="B48" s="2" t="str">
-        <v>조도윤</v>
+        <v>홍도윤</v>
       </c>
       <c r="C48" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D48" s="2">
-        <v>86</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <v/>
+        <v>69</v>
+      </c>
+      <c r="E48" s="2">
+        <v>3</v>
       </c>
       <c r="F48" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G48" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="49">
@@ -1414,19 +1559,22 @@
         <v>47</v>
       </c>
       <c r="B49" s="2" t="str">
-        <v>류하은</v>
+        <v>서민서</v>
       </c>
       <c r="C49" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D49" s="2">
-        <v>60</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E49" s="2">
+        <v>5</v>
       </c>
       <c r="F49" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="50">
@@ -1434,19 +1582,22 @@
         <v>48</v>
       </c>
       <c r="B50" s="2" t="str">
-        <v>윤예준</v>
+        <v>오예준</v>
       </c>
       <c r="C50" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D50" s="2">
-        <v>59</v>
-      </c>
-      <c r="E50" s="2" t="str">
-        <v/>
+        <v>89</v>
+      </c>
+      <c r="E50" s="2">
+        <v>5</v>
       </c>
       <c r="F50" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G50" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="51">
@@ -1454,18 +1605,21 @@
         <v>49</v>
       </c>
       <c r="B51" s="2" t="str">
-        <v>강민서</v>
+        <v>조지유</v>
       </c>
       <c r="C51" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D51" s="2">
-        <v>79</v>
-      </c>
-      <c r="E51" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E51" s="2">
+        <v>1</v>
       </c>
       <c r="F51" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G51" s="2" t="str">
         <v>3반</v>
       </c>
     </row>
@@ -1474,19 +1628,22 @@
         <v>50</v>
       </c>
       <c r="B52" s="2" t="str">
-        <v>김시우</v>
+        <v>안시우</v>
       </c>
       <c r="C52" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D52" s="2">
-        <v>94</v>
-      </c>
-      <c r="E52" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E52" s="2">
+        <v>4</v>
       </c>
       <c r="F52" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G52" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="53">
@@ -1494,18 +1651,21 @@
         <v>51</v>
       </c>
       <c r="B53" s="2" t="str">
-        <v>홍지유</v>
+        <v>이채원</v>
       </c>
       <c r="C53" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D53" s="2">
-        <v>81</v>
-      </c>
-      <c r="E53" s="2" t="str">
-        <v/>
+        <v>67</v>
+      </c>
+      <c r="E53" s="2">
+        <v>4</v>
       </c>
       <c r="F53" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G53" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -1514,19 +1674,22 @@
         <v>52</v>
       </c>
       <c r="B54" s="2" t="str">
-        <v>류하준</v>
+        <v>신하준</v>
       </c>
       <c r="C54" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D54" s="2">
-        <v>68</v>
-      </c>
-      <c r="E54" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E54" s="2">
+        <v>1</v>
       </c>
       <c r="F54" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G54" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="55">
@@ -1534,18 +1697,21 @@
         <v>53</v>
       </c>
       <c r="B55" s="2" t="str">
-        <v>강윤서</v>
+        <v>장수아</v>
       </c>
       <c r="C55" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D55" s="2">
-        <v>86</v>
-      </c>
-      <c r="E55" s="2" t="str">
-        <v/>
+        <v>88</v>
+      </c>
+      <c r="E55" s="2">
+        <v>1</v>
       </c>
       <c r="F55" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G55" s="2" t="str">
         <v>3반</v>
       </c>
     </row>
@@ -1554,19 +1720,22 @@
         <v>54</v>
       </c>
       <c r="B56" s="2" t="str">
-        <v>윤주원</v>
+        <v>최주원</v>
       </c>
       <c r="C56" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D56" s="2">
-        <v>73</v>
-      </c>
-      <c r="E56" s="2" t="str">
-        <v/>
+        <v>96</v>
+      </c>
+      <c r="E56" s="2">
+        <v>5</v>
       </c>
       <c r="F56" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G56" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="57">
@@ -1574,19 +1743,22 @@
         <v>55</v>
       </c>
       <c r="B57" s="2" t="str">
-        <v>서채원</v>
+        <v>박지민</v>
       </c>
       <c r="C57" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D57" s="2">
-        <v>94</v>
-      </c>
-      <c r="E57" s="2" t="str">
-        <v/>
+        <v>88</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G57" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="58">
@@ -1594,19 +1766,22 @@
         <v>56</v>
       </c>
       <c r="B58" s="2" t="str">
-        <v>오지호</v>
+        <v>안지호</v>
       </c>
       <c r="C58" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D58" s="2">
-        <v>89</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="E58" s="2">
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G58" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="59">
@@ -1614,19 +1789,22 @@
         <v>57</v>
       </c>
       <c r="B59" s="2" t="str">
-        <v>황수아</v>
+        <v>최예은</v>
       </c>
       <c r="C59" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D59" s="2">
-        <v>80</v>
-      </c>
-      <c r="E59" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E59" s="2">
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G59" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="60">
@@ -1634,19 +1812,22 @@
         <v>58</v>
       </c>
       <c r="B60" s="2" t="str">
-        <v>안지후</v>
+        <v>오지후</v>
       </c>
       <c r="C60" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D60" s="2">
-        <v>79</v>
-      </c>
-      <c r="E60" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E60" s="2">
+        <v>4</v>
       </c>
       <c r="F60" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G60" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="61">
@@ -1654,19 +1835,22 @@
         <v>59</v>
       </c>
       <c r="B61" s="2" t="str">
-        <v>조지민</v>
+        <v>송다은</v>
       </c>
       <c r="C61" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D61" s="2">
-        <v>72</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <v/>
+        <v>77</v>
+      </c>
+      <c r="E61" s="2">
+        <v>2</v>
       </c>
       <c r="F61" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G61" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="62">
@@ -1674,19 +1858,22 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="str">
-        <v>황준우</v>
+        <v>오준우</v>
       </c>
       <c r="C62" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D62" s="2">
-        <v>76</v>
-      </c>
-      <c r="E62" s="2" t="str">
-        <v>✓</v>
+        <v>78</v>
+      </c>
+      <c r="E62" s="2">
+        <v>3</v>
       </c>
       <c r="F62" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G62" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="63">
@@ -1694,19 +1881,22 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="str">
-        <v>신예은</v>
+        <v>홍하린</v>
       </c>
       <c r="C63" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D63" s="2">
-        <v>68</v>
-      </c>
-      <c r="E63" s="2" t="str">
-        <v/>
+        <v>83</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
       </c>
       <c r="F63" s="2" t="str">
-        <v>2반</v>
+        <v>✓</v>
+      </c>
+      <c r="G63" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="64">
@@ -1720,12 +1910,15 @@
         <v>남</v>
       </c>
       <c r="D64" s="2">
-        <v>88</v>
-      </c>
-      <c r="E64" s="2" t="str">
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="E64" s="2">
+        <v>3</v>
       </c>
       <c r="F64" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G64" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1734,19 +1927,22 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="str">
-        <v>서다은</v>
+        <v>김소율</v>
       </c>
       <c r="C65" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D65" s="2">
-        <v>88</v>
-      </c>
-      <c r="E65" s="2" t="str">
-        <v/>
+        <v>72</v>
+      </c>
+      <c r="E65" s="2">
+        <v>3</v>
       </c>
       <c r="F65" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G65" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="66">
@@ -1754,19 +1950,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="str">
-        <v>조우진</v>
+        <v>안우진</v>
       </c>
       <c r="C66" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D66" s="2">
-        <v>81</v>
-      </c>
-      <c r="E66" s="2" t="str">
-        <v/>
+        <v>76</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
       </c>
       <c r="F66" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G66" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="67">
@@ -1774,19 +1973,22 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="str">
-        <v>황하린</v>
+        <v>류유나</v>
       </c>
       <c r="C67" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D67" s="2">
-        <v>74</v>
-      </c>
-      <c r="E67" s="2" t="str">
-        <v/>
+        <v>84</v>
+      </c>
+      <c r="E67" s="2">
+        <v>2</v>
       </c>
       <c r="F67" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G67" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="68">
@@ -1800,13 +2002,16 @@
         <v>남</v>
       </c>
       <c r="D68" s="2">
-        <v>79</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
       </c>
       <c r="F68" s="2" t="str">
-        <v>2반</v>
+        <v/>
+      </c>
+      <c r="G68" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="69">
@@ -1814,18 +2019,21 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="str">
-        <v>최소율</v>
+        <v>박시은</v>
       </c>
       <c r="C69" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D69" s="2">
-        <v>72</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <v/>
+        <v>78</v>
+      </c>
+      <c r="E69" s="2">
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G69" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -1834,19 +2042,22 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="str">
-        <v>오현우</v>
+        <v>안현우</v>
       </c>
       <c r="C70" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D70" s="2">
-        <v>80</v>
-      </c>
-      <c r="E70" s="2" t="str">
-        <v/>
+        <v>81</v>
+      </c>
+      <c r="E70" s="2">
+        <v>4</v>
       </c>
       <c r="F70" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G70" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="71">
@@ -1854,18 +2065,21 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="str">
-        <v>임유나</v>
+        <v>장예린</v>
       </c>
       <c r="C71" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D71" s="2">
-        <v>77</v>
-      </c>
-      <c r="E71" s="2" t="str">
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
       </c>
       <c r="F71" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G71" s="2" t="str">
         <v>4반</v>
       </c>
     </row>
@@ -1874,19 +2088,22 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="str">
-        <v>안연우</v>
+        <v>강연우</v>
       </c>
       <c r="C72" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D72" s="2">
-        <v>89</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <v/>
+        <v>73</v>
+      </c>
+      <c r="E72" s="2">
+        <v>4</v>
       </c>
       <c r="F72" s="2" t="str">
-        <v>3반</v>
+        <v/>
+      </c>
+      <c r="G72" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
     <row r="73">
@@ -1894,19 +2111,22 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="str">
-        <v>정시은</v>
+        <v>홍지안</v>
       </c>
       <c r="C73" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D73" s="2">
-        <v>81</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2</v>
       </c>
       <c r="F73" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G73" s="2" t="str">
+        <v>4반</v>
       </c>
     </row>
     <row r="74">
@@ -1920,13 +2140,16 @@
         <v>남</v>
       </c>
       <c r="D74" s="2">
-        <v>78</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E74" s="2">
+        <v>5</v>
       </c>
       <c r="F74" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G74" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="75">
@@ -1934,18 +2157,21 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="str">
-        <v>최예린</v>
+        <v>서서아</v>
       </c>
       <c r="C75" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D75" s="2">
-        <v>77</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <v/>
+        <v>70</v>
+      </c>
+      <c r="E75" s="2">
+        <v>4</v>
       </c>
       <c r="F75" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G75" s="2" t="str">
         <v>2반</v>
       </c>
     </row>
@@ -1954,19 +2180,22 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="str">
-        <v>오정우</v>
+        <v>홍정우</v>
       </c>
       <c r="C76" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D76" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
       </c>
       <c r="F76" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G76" s="2" t="str">
+        <v>2반</v>
       </c>
     </row>
     <row r="77">
@@ -1974,19 +2203,22 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="str">
-        <v>안지안</v>
+        <v>최나은</v>
       </c>
       <c r="C77" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D77" s="2">
-        <v>71</v>
-      </c>
-      <c r="E77" s="2" t="str">
-        <v/>
+        <v>63</v>
+      </c>
+      <c r="E77" s="2">
+        <v>3</v>
       </c>
       <c r="F77" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G77" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="78">
@@ -1994,19 +2226,22 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="str">
-        <v>조승현</v>
+        <v>신승현</v>
       </c>
       <c r="C78" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D78" s="2">
-        <v>84</v>
-      </c>
-      <c r="E78" s="2" t="str">
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3</v>
       </c>
       <c r="F78" s="2" t="str">
-        <v>1반</v>
+        <v/>
+      </c>
+      <c r="G78" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="79">
@@ -2014,18 +2249,21 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="str">
-        <v>윤서아</v>
+        <v>최지우</v>
       </c>
       <c r="C79" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D79" s="2">
-        <v>82</v>
-      </c>
-      <c r="E79" s="2" t="str">
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="E79" s="2">
+        <v>4</v>
       </c>
       <c r="F79" s="2" t="str">
+        <v/>
+      </c>
+      <c r="G79" s="2" t="str">
         <v>1반</v>
       </c>
     </row>
@@ -2034,19 +2272,22 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="str">
-        <v>송민재</v>
+        <v>안민재</v>
       </c>
       <c r="C80" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D80" s="2">
-        <v>70</v>
-      </c>
-      <c r="E80" s="2" t="str">
-        <v/>
+        <v>75</v>
+      </c>
+      <c r="E80" s="2">
+        <v>4</v>
       </c>
       <c r="F80" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G80" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="81">
@@ -2054,19 +2295,22 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="str">
-        <v>조나은</v>
+        <v>신서윤</v>
       </c>
       <c r="C81" s="2" t="str">
         <v>여</v>
       </c>
       <c r="D81" s="2">
-        <v>67</v>
-      </c>
-      <c r="E81" s="2" t="str">
-        <v/>
+        <v>74</v>
+      </c>
+      <c r="E81" s="2">
+        <v>3</v>
       </c>
       <c r="F81" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G81" s="2" t="str">
+        <v>3반</v>
       </c>
     </row>
     <row r="82">
@@ -2074,24 +2318,27 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="str">
-        <v>신지환</v>
+        <v>황지환</v>
       </c>
       <c r="C82" s="2" t="str">
         <v>남</v>
       </c>
       <c r="D82" s="2">
-        <v>86</v>
-      </c>
-      <c r="E82" s="2" t="str">
-        <v/>
+        <v>79</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2</v>
       </c>
       <c r="F82" s="2" t="str">
-        <v>4반</v>
+        <v/>
+      </c>
+      <c r="G82" s="2" t="str">
+        <v>1반</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F82"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G82"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2102,13 +2349,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B1" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C1" s="2">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -2124,21 +2371,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B1" s="2">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2">
-        <v>68</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2146,4 +2393,84 @@
     <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="str">
+        <v>항목</v>
+      </c>
+      <c r="B1" s="2" t="str">
+        <v>종류</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <v>선택지</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>성별</v>
+      </c>
+      <c r="B2" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <v>남</v>
+      </c>
+      <c r="D2" s="2" t="str">
+        <v>여</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>학업 성취도</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>숫자</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>국어 수준</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>정도</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>학습 지원</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>체크</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>이전 반</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>목록</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>1반</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>2반</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>3반</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <v>4반</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+  </ignoredErrors>
+</worksheet>
 </file>